--- a/UNEMPLOYMENT_10092026/Africa_Unemployment_Collector_Progress_Report.xlsx
+++ b/UNEMPLOYMENT_10092026/Africa_Unemployment_Collector_Progress_Report.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Outstanding &amp; Next Steps" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Country Status'!$A$1:$N$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Country Status'!$A$1:$N$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -469,7 +469,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated: 10 September 2026</t>
+          <t>Generated: 27 September 2026</t>
         </is>
       </c>
     </row>
@@ -486,7 +486,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>As at this reporting date, 26 countries are collected and validated, yielding 11,093 rows. Coverage runs from South Africa's 74 quarters (2008 Q1 to 2026 Q2) through quarterly series for Egypt, Ghana, Mauritius, Tunisia and others, to single ad-hoc rounds where that is all an NSO has published. 2 countries are outstanding, both for reasons outside the collector's control.</t>
+          <t>As at this reporting date, 28 countries are collected and validated, yielding 14,682 rows. Coverage runs from South Africa's 74 quarters (2008 Q1 to 2026 Q2) through quarterly series for Egypt, Ghana, Mauritius, Tunisia and others, to single ad-hoc rounds where that is all an NSO has published. 0 countries are outstanding, both for reasons outside the collector's control.</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>This report also records a class of defect worth stating plainly. Four descriptors were downloading the wrong publication, and six countries were producing values that looked entirely reasonable but came from the wrong column, the wrong table or the wrong year. All were found by checking output against the figures the reports themselves print, and every country module now carries those cross-check values so the same drift is caught on the next run.</t>
+          <t>THE OFFLINE SUITE NOW COVERS KENYA, the country this round rebuilt from 17 rows to 464. Three of its four new checks target failures a validator cannot see: the List of Tables opening a block that outlived its page, which made Table 3 publish the labour force as employment and the participation rate as the employment ratio; the ten age cohorts across three quarters, two of which exist in no other source the collector reads; and the report's own LU2 contradiction, preserved rather than resolved. The fourth closes a gap in the harness itself -- the parser prints unmatched row specs and carries on, so a suite could stay green while a layout quietly stopped matching; where a fixture is a whole table, zero misses is now asserted. This report also records a class of defect worth stating plainly. Four descriptors were downloading the wrong publication, and six countries were producing values that looked entirely reasonable but came from the wrong column, the wrong table or the wrong year. All were found by checking output against the figures the reports themselves print, and every country module now carries those cross-check values so the same drift is caught on the next run.</t>
         </is>
       </c>
     </row>
@@ -517,21 +517,21 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Countries collected: 26</t>
+          <t>Countries collected: 28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Countries outstanding: 2</t>
+          <t>Countries outstanding: 0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Total rows: 11,093</t>
+          <t>Total rows: 14,682</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -671,63 +671,63 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BEN</t>
+          <t>AGO</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>West Africa (WAEMU)</t>
+          <t>Southern (SADC)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Collected</t>
+          <t>Collected — unblocked, two methodologies, 18 provinces</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NSO (INStaD)</t>
+          <t>NSO (INE Angola)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ERI-ESI 2018</t>
+          <t>IEA — Séries cronológicas, quadros complementares, indicadores por província</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ad_hoc</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>108</v>
+        <v>2870</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2018 to 2018</t>
+          <t>2019 to 2026-Q2</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>static_url (Tier-3 report)</t>
+          <t>ine_ao_directory_files (Tier-2 structured file)</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>ERI-ESI table is transposed and interleaves two 'Effectif' columns</t>
+          <t>Blocked since INE replaced the IEA bulletin PDF with workbooks fetched only by POSTing a file path to /Diretorios/Download, behind folder links whose tokens change per session. The five workbooks then split at a METHODOLOGY BREAK — 13th ICLS to 2025 Q3 (participation 87-89%, own-use production counted as work) and 19th-21st ICLS from 2025 Q4 (participation 50-56%) — and the complementary workbook REPEATS the headline cells of the series workbook, five of them differing by up to 0,05 points (2022 annual youth, 2025 Q4 headline), the signature of a reweighting applied to one file only</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Column set declared per row; no participation rate exists in the source, so none is invented</t>
+          <t>POST support in core/fetch and a discovery method walking INE's tree by folder name, each file pattern required to match exactly one workbook. Headline series in three blocks (15+, the 15-24 youth cut, and an 18+ base), rates by residence, sex and age, and an annual table for the 18 provinces whose labour forces are checked to sum to the national figure. Each row names its ICLS basis in `survey`. The repeated cells are treated as a CHECK, never a second row: the series workbook's value is kept, a gap up to 0,1 points is tolerated and any larger gap raises. 2,870 rows over 32 periods, 2019 to 2026 Q2 — replacing a layout that read one quarter per bulletin</t>
         </is>
       </c>
     </row>
@@ -737,17 +737,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>BEN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Southern (SADC)</t>
+          <t>West Africa (WAEMU)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -757,43 +757,43 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NSO (Statistics Botswana)</t>
+          <t>NSO (INStaD)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>QMTS Labour Force Module</t>
+          <t>ERI-ESI 2018</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>ad_hoc</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>51</v>
+        <v>108</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2024-Q1 to 2024-Q1</t>
+          <t>2018 to 2018</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>page_scrape (Tier-3 report)</t>
+          <t>static_url (Tier-3 report)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Listing page is the whole labour catalogue, newest-first — a 'labour force' match downloaded the BMTHS, a DIFFERENT survey the notes forbid chaining; every row is also prefixed with its printed index, so no ^-anchored pattern matched</t>
+          <t>ERI-ESI table is transposed and interleaves two 'Effectif' columns</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Match on 'quarterly' + 'labour force module'; new strip_row_number option removes the index from text and numbers at once</t>
+          <t>Column set declared per row; no participation rate exists in the source, so none is invented</t>
         </is>
       </c>
     </row>
@@ -803,17 +803,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BFA</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>West Africa (WAEMU)</t>
+          <t>Southern (SADC)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -823,28 +823,28 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NSO (INSD)</t>
+          <t>NSO (Statistics Botswana)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ENB-ESI 2023</t>
+          <t>QMTS Labour Force Module</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ad_hoc</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2023 to 2023</t>
+          <t>2024-Q1 to 2024-Q1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -854,12 +854,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Every link on the INSD page is captioned 'Telecharger', so a match on 'emploi' took the ENSE bulletin the layout's own notes call charts-only</t>
+          <t>Listing page is the whole labour catalogue, newest-first — a 'labour force' match downloaded the BMTHS, a DIFFERENT survey the notes forbid chaining; every row is also prefixed with its printed index, so no ^-anchored pattern matched</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Select by filename ('note_synth' + 'secteurinformel'); anchor the table on its caption, since 'Taux de chomage' is split across two header lines</t>
+          <t>Match on 'quarterly' + 'labour force module'; new strip_row_number option removes the index from text and numbers at once</t>
         </is>
       </c>
     </row>
@@ -869,17 +869,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CMR</t>
+          <t>BFA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Central Africa (CEMAC)</t>
+          <t>West Africa (WAEMU)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -889,12 +889,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NSO (INS Cameroun)</t>
+          <t>NSO (INSD)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>EESI3</t>
+          <t>ENB-ESI 2023</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -903,29 +903,29 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2022 to 2022</t>
+          <t>2023 to 2023</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>static_url (Tier-3 report)</t>
+          <t>page_scrape (Tier-3 report)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Two-column depliant: every extracted line splices both columns, so urban unemployment was read as 93.3% — an informal-employment share from the neighbouring table</t>
+          <t>Every link on the INSD page is captioned 'Telecharger', so a match on 'emploi' took the ENSE bulletin the layout's own notes call charts-only</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>New split_columns option crops each page into its printed columns before reading</t>
+          <t>Select by filename ('note_synth' + 'secteurinformel'); anchor the table on its caption, since 'Taux de chomage' is split across two header lines</t>
         </is>
       </c>
     </row>
@@ -935,17 +935,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EGY</t>
+          <t>CMR</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Central Africa (CEMAC)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -955,43 +955,43 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NSO (CAPMAS)</t>
+          <t>NSO (INS Cameroun)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>LFS quarterly bulletin (publication id 11)</t>
+          <t>EESI3</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>ad_hoc</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>192</v>
+        <v>30</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-Q2 to 2026-Q2</t>
+          <t>2022 to 2022</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>capmas_publication (Tier-1 API)</t>
+          <t>static_url (Tier-3 report)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>CAPMAS publishes Excel or PDF per issue; discovery silently fell back to PDF under a .xlsx filename. The PDF is right-to-left, so its columns run Total, Females, Males — the REVERSE of the workbook</t>
+          <t>Two-column depliant: every extracted line splices both columns, so urban unemployment was read as 93.3% — an informal-employment share from the neighbouring table</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Format substitution now refused by name; layout reads the PDF with the printed column order and is cross-checked on female &gt;&gt; male unemployment</t>
+          <t>New split_columns option crops each page into its printed columns before reading</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SWZ</t>
+          <t>EGY</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Southern (SADC)</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1021,43 +1021,43 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NSO (CSO)</t>
+          <t>NSO (CAPMAS)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ILFS 2023</t>
+          <t>LFS quarterly bulletin (publication id 11)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ad_hoc</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>72</v>
+        <v>192</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2023 to 2023</t>
+          <t>2026-Q2 to 2026-Q2</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>static_url (Tier-3 report)</t>
+          <t>capmas_publication (Tier-1 API)</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>A shared Male|Female|Total column vocabulary also carried locality:all, which overwrote the rows' own Urban/Rural and published both as extra national figures</t>
+          <t>CAPMAS publishes Excel or PDF per issue; discovery silently fell back to PDF under a .xlsx filename. The PDF is right-to-left, so its columns run Total, Females, Males — the REVERSE of the workbook</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Column vocabulary reduced to sex only; locality now comes from the row, as the table intends</t>
+          <t>Format substitution now refused by name; layout reads the PDF with the printed column order and is cross-checked on female &gt;&gt; male unemployment</t>
         </is>
       </c>
     </row>
@@ -1067,17 +1067,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>SWZ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Horn of Africa</t>
+          <t>Southern (SADC)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NSO (ESS)</t>
+          <t>NSO (Central Statistical Office)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>LMS</t>
+          <t>ILFS 2023</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1101,14 +1101,14 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2021 to 2021</t>
+          <t>2023 to 2023</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>10+ working-age base — the lowest in Africa; Tigray excluded from the round</t>
+          <t>A shared Male|Female|Total column vocabulary also carried locality:all, which overwrote the rows' own Urban/Rural and published both as extra national figures</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Base travels on every row; the coverage gap is recorded in the descriptor rather than patched</t>
+          <t>Column vocabulary reduced to sex only; locality now comes from the row, as the table intends</t>
         </is>
       </c>
     </row>
@@ -1133,63 +1133,63 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GHA</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Horn of Africa</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Collected — Tier 1</t>
+          <t>Collected</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>NSO (GSS)</t>
+          <t>NSO (ESS)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AHIES</t>
+          <t>LMS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>ad_hoc</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6426</v>
+        <v>120</v>
       </c>
       <c r="J9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2022-Q1 to 2023-Q3</t>
+          <t>2021 to 2021</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>static_url (Tier-1 API)</t>
+          <t>static_url (Tier-3 report)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>The only machine-readable NSO labour source in Africa; the API lags the country's own releases</t>
+          <t>10+ working-age base — the lowest in Africa; Tigray excluded from the round</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>PxWeb reader; the lag is the source's, and is reported rather than filled</t>
+          <t>Base travels on every row; the coverage gap is recorded in the descriptor rather than patched</t>
         </is>
       </c>
     </row>
@@ -1199,63 +1199,63 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Guinea Bissau</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GNB</t>
+          <t>GHA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>West Africa (WAEMU)</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Collected</t>
+          <t>Collected — Tier 1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NSO (INE Guiné-Bissau)</t>
+          <t>NSO (GSS)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ERI-ESI / IRIESI 2017-2018</t>
+          <t>AHIES + PHC 2021</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ad_hoc</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>80</v>
+        <v>6477</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2018 to 2018</t>
+          <t>2021 to 2023-Q3</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>static_url (Tier-3 report)</t>
+          <t>NSO data API, 2 table(s) (Tier-1 API) + NSO data API, 1 table(s) (Tier-1 API)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Repeated block heading left the block open into the NEXT indicator, and the age rows print on their own lines rather than as a suffix</t>
+          <t>The only machine-readable NSO labour source in Africa; the API lags the country's own releases</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Blocks now close at the next heading once they have data; age rows scoped by block</t>
+          <t>PxWeb reader; the lag is the source's, and is reported rather than filled</t>
         </is>
       </c>
     </row>
@@ -1265,48 +1265,48 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Guinea Bissau</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>KEN</t>
+          <t>GNB</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>East Africa (EAC)</t>
+          <t>West Africa (WAEMU)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Collected — historical backfill</t>
+          <t>Collected</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>NSO (KNBS)</t>
+          <t>NSO (INE Guiné-Bissau)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>QLFS</t>
+          <t>ERI-ESI / IRIESI 2017-2018</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>ad_hoc</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2022-Q4 to 2022-Q4</t>
+          <t>2018 to 2018</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Leader dots after every label defeated five row patterns; three labels had been guessed rather than read; the split header dated the release to Q4 2021 instead of Q4 2022</t>
+          <t>Repeated block heading left the block open into the NEXT indicator, and the age rows print on their own lines rather than as a suffix</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Patterns anchored on the printed labels and their dots; period pinned, since KNBS discontinued the series after this issue</t>
+          <t>Blocks now close at the next heading once they have data; age rows scoped by block</t>
         </is>
       </c>
     </row>
@@ -1331,63 +1331,63 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MLI</t>
+          <t>KEN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>West Africa (WAEMU)</t>
+          <t>East Africa (EAC)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Collected</t>
+          <t>Collected — historical backfill, fully disaggregated</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>NSO (INSTAT Mali)</t>
+          <t>NSO (KNBS)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bulletin des indicateurs du marché du travail</t>
+          <t>QLFS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ad_hoc</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>464</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2022 to 2022</t>
+          <t>2021-Q4 to 2022-Q4</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>page_scrape (Tier-3 report)</t>
+          <t>static_url (Tier-3 report)</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>The summary is an INFOGRAPHIC — two captions share a line while their values sit two lines below, so no line-based reader can pair them</t>
+          <t>Leader dots after every label defeated five row patterns; three labels had been guessed rather than read; the split header dated the release to Q4 2021 instead of Q4 2022. And the report was being read at a twentieth of its depth: Table 1's national headline was captured while Tables 2-9b, which repeat every series for TEN AGE COHORTS across THREE QUARTERS, were left entirely. Those earlier quarters are carried by no other source, because KNBS archived the QLFS after 2022 Q4 and this descriptor fetches that single file</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Bespoke reader that pairs each caption with the value beneath it by glyph position, then asserts the box's own arithmetic</t>
+          <t>Patterns anchored on the printed labels and their dots; period pinned, since KNBS discontinued the series after this issue. The age tables are now read as well — 17 rows became 464, eleven age groups across 2021 Q4, 2022 Q3 and 2022 Q4 — with each quarter's column group carrying its own period. TWO TRAPS ON THE WAY: tables share pages (2 and 3 on page 7, 4 and 5 on page 9) with identical '15-19' labels, so blocks keyed on each caption separate them; and block context outlives its page, so the List of Tables' dot-leader entry opened a block that was still open on the real page, making Table 3 publish the LABOUR FORCE as employment and the PARTICIPATION rate as the employment ratio — real values in the wrong series, which nothing downstream could catch. Fixed by excluding the contents pages and requiring captions not to be followed by dot leaders. The report's LU2 contradiction is preserved rather than resolved: Table 1 says 18.6 per cent, Table 6 and the prose say 9.0, and Table 1's companion count is exactly twice what its own footnote defines — both are kept, told apart by the label each table prints</t>
         </is>
       </c>
     </row>
@@ -1397,63 +1397,63 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MUS</t>
+          <t>LBR</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Southern (SADC)/Islands</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Collected</t>
+          <t>Collected — restored through LISGIS's new API</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>NSO (Ministry of Finance)</t>
+          <t>NSO (LISGIS)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CMPHS</t>
+          <t>LBR-LFS 2016-2017</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>ad_hoc</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="J13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2025-Q1 to 2026-Q1</t>
+          <t>2017 to 2017</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>two_hop_scrape (Tier-2 structured file)</t>
+          <t>static_url (Tier-3 report)</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Workbook is TRANSPOSED relative to the wide-series model — periods run down column A — so all nine sheets reported 'no period header row'</t>
+          <t>LISGIS's old site had become a placeholder linking only to an aggregator, so Liberia sat in sources_blocked. The rebuilt site serves the LFS 2016-17 report again, but this copy's text layer wraps Table 3.1's row labels across up to four lines and puts the LU rows on an uncaptioned continuation page; the kept line-matching layout then read the informal-employment COUNT (467,318) as the informal-employment share</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Bespoke reader for Tables 1 and 2; published rates taken as printed, never divided out</t>
+          <t>Table 3.1 is read by POSITION: every data row prints exactly seventeen numbers in a fixed order, and the mapping is proved in all seventeen columns by the table's own identities (labour force = employed + unemployed, population = labour force + outside, LU1 = unemployed / labour force, participation = labour force / population), with an offline test that swaps two rows and must see the read fail. All cross-check totals reproduce, including the report's own suspect LU4 of 78.0 for persons with a functional difficulty, which stays flagged rather than corrected. LU2 is now collected as well</t>
         </is>
       </c>
     </row>
@@ -1463,48 +1463,48 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>MLI</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>West Africa (WAEMU)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Collected — headline</t>
+          <t>Collected</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>NSO (HCP)</t>
+          <t>NSO (INSTAT Mali)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Activité, emploi et chômage — résultats annuels</t>
+          <t>Bulletin des indicateurs du marché du travail</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>ad_hoc</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2025 to 2025</t>
+          <t>2022 to 2022</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Row labels wrap around their own numbers, two different ways on one page; the page anchor matched only the activity table, never the unemployment one</t>
+          <t>The summary is an INFOGRAPHIC — two captions share a line while their values sit two lines below, so no line-based reader can pair them</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Two anchored tables plus wrapped-label rejoining. The age breakdown is deliberately NOT read — see the module note</t>
+          <t>Bespoke reader that pairs each caption with the value beneath it by glyph position, then asserts the box's own arithmetic</t>
         </is>
       </c>
     </row>
@@ -1529,17 +1529,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NAM</t>
+          <t>MUS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Southern (SADC)</t>
+          <t>Southern (SADC)/Islands</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1549,43 +1549,43 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>NSO (NSA)</t>
+          <t>NSO (Ministry of Finance)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>PHC 2023 Labour Force Report</t>
+          <t>CMPHS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>ad_hoc</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>45</v>
+        <v>204</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2023 to 2023</t>
+          <t>2025-Q1 to 2026-Q1</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>two_hop_scrape (Tier-3 report)</t>
+          <t>two_hop_scrape (Tier-2 structured file)</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>The caption on the table page renders with every letter doubled, so the anchor found only the contents page; several cells are letter-spaced ('3 6 . 9')</t>
+          <t>Workbook is TRANSPOSED relative to the wide-series model — periods run down column A — so all nine sheets reported 'no period header row'</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Anchor on the header row instead; new despace_numbers rejoins letter-spaced values</t>
+          <t>Bespoke reader for Tables 1 and 2; published rates taken as printed, never divided out</t>
         </is>
       </c>
     </row>
@@ -1595,63 +1595,63 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Niger</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NER</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>West Africa (WAEMU)</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Collected</t>
+          <t>Collected — headline</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>NSO (INS Niger)</t>
+          <t>NSO (HCP)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ERI-ESI 2017</t>
+          <t>Activité, emploi et chômage — résultats annuels</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ad_hoc</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2017 to 2017</t>
+          <t>2025 to 2025</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>static_url (Tier-3 report)</t>
+          <t>page_scrape (Tier-3 report)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>A repeated heading left its block open into 'Duree moyenne de chomage', so 6.65 YEARS was published as a 6.65% underutilisation rate</t>
+          <t>Row labels wrap around their own numbers, two different ways on one page; the page anchor matched only the activity table, never the unemployment one</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Blocks close at the next heading; the age rows that belong under the repeat are now captured, which also closes it</t>
+          <t>Two anchored tables plus wrapped-label rejoining. The age breakdown is deliberately NOT read — see the module note</t>
         </is>
       </c>
     </row>
@@ -1661,17 +1661,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NGA</t>
+          <t>NAM</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>Southern (SADC)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1681,43 +1681,43 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>NSO (NBS)</t>
+          <t>NSO (NSA)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>NLFS</t>
+          <t>PHC 2023 Labour Force Report</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>ad_hoc</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2024-Q2 to 2024-Q2</t>
+          <t>2023 to 2023</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>table_row_link (Tier-3 report)</t>
+          <t>two_hop_scrape (Tier-3 report)</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>The e-library is a DataTable: the title and the link sit in different cells and the link's text is an icon, so a link-text scrape matched none of fifteen entries</t>
+          <t>The caption on the table page renders with every letter doubled, so the anchor found only the contents page; several cells are letter-spaced ('3 6 . 9')</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>New table_row_link method matches the ROW and takes its link; 'socio-economic' separates data releases from the reference documents filed beside them</t>
+          <t>Anchor on the header row instead; new despace_numbers rejoins letter-spaced values</t>
         </is>
       </c>
     </row>
@@ -1727,17 +1727,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Niger</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>RWA</t>
+          <t>NER</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>East Africa (EAC)</t>
+          <t>West Africa (WAEMU)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1747,43 +1747,43 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>NSO (NISR)</t>
+          <t>NSO (INS Niger)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>LFS</t>
+          <t>ERI-ESI 2017</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>ad_hoc</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="J18" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2019 to 2025</t>
+          <t>2017 to 2017</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>chain_scrape (Tier-3 report)</t>
+          <t>static_url (Tier-3 report)</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Three of the trend table's labels wrap around their own numbers; the newest LFS year page has no annual report yet, so a two-hop walk stopped at a dead end</t>
+          <t>A repeated heading left its block open into 'Duree moyenne de chomage', so 6.65 YEARS was published as a 6.65% underutilisation rate</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>New chain_scrape backtracks to the most recent year that HAS the report; wrapped labels rejoined</t>
+          <t>Blocks close at the next heading; the age rows that belong under the repeat are now captured, which also closes it</t>
         </is>
       </c>
     </row>
@@ -1793,17 +1793,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SYC</t>
+          <t>NGA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Islands</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1813,12 +1813,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NSO (NBS Seychelles)</t>
+          <t>NSO (National Bureau of Statistics)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>LFS Bulletin</t>
+          <t>NLFS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1827,29 +1827,29 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-Q1 to 2026-Q1</t>
+          <t>2024-Q2 to 2024-Q2</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>two_hop_scrape (Tier-3 report)</t>
+          <t>table_row_link (Tier-3 report)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>The rates block sits directly beneath a block of sex shares</t>
+          <t>The e-library is a DataTable: the title and the link sit in different cells and the link's text is an icon, so a link-text scrape matched none of fifteen entries</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Page anchored on the rates block; values cross-checked against the bulletin</t>
+          <t>New table_row_link method matches the ROW and takes its link; 'socio-economic' separates data releases from the reference documents filed beside them</t>
         </is>
       </c>
     </row>
@@ -1859,63 +1859,63 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SLE</t>
+          <t>RWA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>West Africa</t>
+          <t>East Africa (EAC)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Collected — stale</t>
+          <t>Collected</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NSO (Stats SL)</t>
+          <t>NSO (NISR)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SLLFS 2014</t>
+          <t>LFS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>ad_hoc</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2014 to 2014</t>
+          <t>2019 to 2025</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>static_url (Tier-3 report)</t>
+          <t>chain_scrape (Tier-3 report)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>15-64 base with a closed upper bound; transposed table; no LFS since 2014</t>
+          <t>Three of the trend table's labels wrap around their own numbers; the newest LFS year page has no annual report yet, so a two-hop walk stopped at a dead end</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Base recorded on every row; the staleness is the source's and is stated, not filled</t>
+          <t>New chain_scrape backtracks to the most recent year that HAS the report; wrapped labels rejoined</t>
         </is>
       </c>
     </row>
@@ -1925,17 +1925,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>SYC</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Horn of Africa</t>
+          <t>Islands</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1945,43 +1945,43 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NSO (SNBS)</t>
+          <t>NSO (NBS Seychelles)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SLFS 2019</t>
+          <t>LFS Bulletin</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>ad_hoc</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2019 to 2019</t>
+          <t>2026-Q1 to 2026-Q1</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>wp_media_named (Tier-3 report)</t>
+          <t>two_hop_scrape (Tier-3 report)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>wp_media_latest orders by a month name in the filename, which a one-off survey report does not have, so the file was discarded as undated</t>
+          <t>The rates block sits directly beneath a block of sex shares</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Switched to wp_media_named; the file named '...Reports-2021' is the 2019 survey, so the period is pinned</t>
+          <t>Page anchored on the rates block; values cross-checked against the bulletin</t>
         </is>
       </c>
     </row>
@@ -1991,63 +1991,63 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ZAF</t>
+          <t>SLE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Southern (SADC)</t>
+          <t>West Africa</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Collected — deepest series</t>
+          <t>Collected — stale</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>NSO (Stats SA)</t>
+          <t>NSO (Stats SL)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>P0211</t>
+          <t>SLLFS 2014</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>ad_hoc</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2886</v>
+        <v>55</v>
       </c>
       <c r="J22" t="n">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2008-Q1 to 2026-Q2</t>
+          <t>2014 to 2014</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>page_scrape (Tier-2 structured file)</t>
+          <t>static_url (Tier-3 report)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>The layout scanned EVERY sheet and took each one's first block, so one national series repeated six times (2,618 rows, 444 distinct) and Table 8's 'Subsistence farming' block was published as the national unemployed count</t>
+          <t>15-64 base with a closed upper bound; transposed table; no LFS since 2014</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Restricted to Table 2 with sex blocks; new Excel block support captures Women and Men; the broad measures are LU1-LU4, not 'expanded', and are now read</t>
+          <t>Base recorded on every row; the staleness is the source's and is stated, not filled</t>
         </is>
       </c>
     </row>
@@ -2057,17 +2057,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Somalia</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TZA</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>East Africa (EAC)</t>
+          <t>Horn of Africa</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2077,43 +2077,43 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>NSO (NBS Tanzania)</t>
+          <t>NSO (SNBS)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ILFS</t>
+          <t>SLFS 2019</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>ad_hoc</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>234</v>
+        <v>60</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2024 to 2025</t>
+          <t>2019 to 2019</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>page_scrape (Tier-3 report)</t>
+          <t>wp_media_named (Tier-3 report)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Table 4.1 prints two years side by side; the period was scanned from page text and matched 'ILFS 2024' in another caption, so 2025's values were published as 2024</t>
+          <t>wp_media_latest orders by a month name in the filename, which a one-off survey report does not have, so the file was discarded as undated</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Both years captured, each column carrying its own period — nothing is inferred from prose</t>
+          <t>Switched to wp_media_named; the file named '...Reports-2021' is the 2019 survey, so the period is pinned</t>
         </is>
       </c>
     </row>
@@ -2123,32 +2123,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TUN</t>
+          <t>ZAF</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>North Africa</t>
+          <t>Southern (SADC)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Collected — Tier 2</t>
+          <t>Collected — deepest series</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>NSO (INS Tunisie)</t>
+          <t>NSO (Stats SA)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>P0201</t>
+          <t>P0211</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2157,29 +2157,29 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>68</v>
+        <v>2886</v>
       </c>
       <c r="J24" t="n">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2024-Q1 to 2026-Q2</t>
+          <t>2008-Q1 to 2026-Q2</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>static_url (Tier-2 structured file)</t>
+          <t>page_scrape (Tier-2 structured file)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>The PDF is bidi-scrambled and unusable</t>
+          <t>The layout scanned EVERY sheet and took each one's first block, so one national series repeated six times (2,618 rows, 444 distinct) and Table 8's 'Subsistence farming' block was published as the national unemployed count</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>INS theme pages read as server-rendered HTML tables, the only correct route</t>
+          <t>Restricted to Table 2 with sex blocks; new Excel block support captures Women and Men; the broad measures are LU1-LU4, not 'expanded', and are now read</t>
         </is>
       </c>
     </row>
@@ -2189,12 +2189,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>TZA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2204,48 +2204,48 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Collected — narrow</t>
+          <t>Collected</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>NSO (UBOS)</t>
+          <t>NSO (NBS Tanzania)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>LMS 2025</t>
+          <t>ILFS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>ad_hoc</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>8</v>
+        <v>234</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2025 to 2025</t>
+          <t>2024 to 2025</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>static_url (Tier-3 report)</t>
+          <t>page_scrape (Tier-3 report)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Both slide headings are letter-spaced ('I n t e r n a t i o n a l'), and one is a suffix of the other</t>
+          <t>Table 4.1 prints two years side by side; the period was scanned from page text and matched 'ILFS 2024' in another caption, so 2025's values were published as 2024</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Anchored on the age-band labels, which are unique per slide and render normally; the rest of the deck is charts and is not scraped</t>
+          <t>Both years captured, each column carrying its own period — nothing is inferred from prose</t>
         </is>
       </c>
     </row>
@@ -2255,63 +2255,63 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ZMB</t>
+          <t>TUN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Southern (SADC)</t>
+          <t>North Africa</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Collected</t>
+          <t>Collected — Tier 2</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>NSO (ZamStats)</t>
+          <t>NSO (INS Tunisie)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>LFS</t>
+          <t>P0201</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2024 to 2024</t>
+          <t>2024-Q1 to 2026-Q2</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>latest_year_file (Tier-3 report)</t>
+          <t>static_url (Tier-2 structured file)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Cleanest PDF of the set; residence prints Rural before Urban, the reverse of Namibia</t>
+          <t>The PDF is bidi-scrambled and unusable</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Column order taken as printed</t>
+          <t>INS theme pages read as server-rendered HTML tables, the only correct route</t>
         </is>
       </c>
     </row>
@@ -2321,68 +2321,200 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ZWE</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Southern (SADC)</t>
+          <t>East Africa (EAC)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Collected</t>
+          <t>Collected — narrow</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>NSO (ZIMSTAT)</t>
+          <t>NSO (UBOS)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>QLFS</t>
+          <t>LMS 2025</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>ad_hoc</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t>2025 to 2025</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>static_url (Tier-3 report)</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Both slide headings are letter-spaced ('I n t e r n a t i o n a l'), and one is a suffix of the other</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Anchored on the age-band labels, which are unique per slide and render normally; the rest of the deck is charts and is not scraped</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Zambia</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ZMB</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Southern (SADC)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>NSO (ZamStats)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>LFS</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>40</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2024 to 2024</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>latest_year_file (Tier-3 report)</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Cleanest PDF of the set; residence prints Rural before Urban, the reverse of Namibia</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Column order taken as printed</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Zimbabwe</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ZWE</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Southern (SADC)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Collected</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>NSO (ZIMSTAT)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>QLFS</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>18</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>2025-Q2 to 2025-Q2</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>page_scrape (Tier-3 report)</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>The /Labor-force/ directory's first PDF is currently a Thematic Report on EDUCATION; it also holds Time Use surveys, an Employment Index and presentation decks</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Match on 'qlfs_report', which the decks and the other products do not carry</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N27"/>
+  <autoFilter ref="A1:N29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2567,7 +2699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2616,76 +2748,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Angola</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>AGO</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Southern (SADC)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Download needs POST</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>INE replaced the IEA bulletin PDF with time-series workbooks reachable only by a POST of `filepath` to /Diretorios/Download. The three-level route to them is resolved and recorded in the descriptor.</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Add POST support to core/fetch, then write a workbook layout. Note the files split on a 13th- vs 19th-ICLS methodology break and must never be chained.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Liberia</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>LBR</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>West Africa</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>NSO no longer hosts</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>lisgis.gov.lr/surveys.php 404s and the site root is a 9 KB placeholder whose only two links both point to Knoema. A hosting failure, not a fetching one.</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Re-probe lisgis.gov.lr for any path other than the two placeholder links. Aggregator copies are excluded by policy.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
